--- a/reports/LoadTesting/Load_Testing_Report.xlsx
+++ b/reports/LoadTesting/Load_Testing_Report.xlsx
@@ -130,7 +130,7 @@
     <t>AI Automation Engine (Enterprise CI/CD)</t>
   </si>
   <si>
-    <t>2026-08-06</t>
+    <t>2026-08-07</t>
   </si>
   <si>
     <t>Screenshots/load-evidence-02.png</t>
